--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FBFC7D-B205-1D41-8056-F100B57909BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7291F594-648E-7F40-B82D-D1619AF5AE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17220" activeTab="5" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="139">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -244,9 +244,6 @@
     <t>TFORM2</t>
   </si>
   <si>
-    <t>TUNIT2</t>
-  </si>
-  <si>
     <t>TBCOL2</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>Column</t>
   </si>
   <si>
-    <t>units: pixels</t>
-  </si>
-  <si>
     <t>Row</t>
   </si>
   <si>
@@ -310,12 +304,6 @@
     <t>Temperature</t>
   </si>
   <si>
-    <t>ms</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>TEMP_TIME</t>
   </si>
   <si>
@@ -328,9 +316,6 @@
     <t>TFORM3</t>
   </si>
   <si>
-    <t>TUNIT3</t>
-  </si>
-  <si>
     <t>TBCOL3</t>
   </si>
   <si>
@@ -473,15 +458,6 @@
   </si>
   <si>
     <t>TableHDU</t>
-  </si>
-  <si>
-    <t>PFVER</t>
-  </si>
-  <si>
-    <t>v1.0.0</t>
-  </si>
-  <si>
-    <t>pandorafits version</t>
   </si>
 </sst>
 </file>
@@ -906,13 +882,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -920,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -931,7 +907,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -939,10 +915,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -950,10 +926,10 @@
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -961,10 +937,10 @@
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -977,7 +953,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81127257-918B-0849-8077-19480435CD41}">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -991,10 +967,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1116,16 +1092,16 @@
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1147,7 +1123,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -1158,7 +1134,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
@@ -1166,40 +1142,40 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B18">
         <v>32</v>
@@ -1210,13 +1186,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1265,90 +1241,90 @@
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C26" s="4">
         <v>65</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>512</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>512</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>1024</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31">
         <v>1024</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1359,7 +1335,7 @@
         <v>200000</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1386,13 +1362,13 @@
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1417,6 +1393,9 @@
         <v>47</v>
       </c>
     </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="5"/>
+    </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
     </row>
@@ -1484,16 +1463,16 @@
       <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="5"/>
+      <c r="A68" s="6"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="5"/>
+      <c r="A70" s="6"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="6"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="5"/>
@@ -1526,25 +1505,22 @@
       <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="5"/>
+      <c r="A82" s="6"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="6"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="5"/>
+      <c r="A84" s="6"/>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="6"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="5"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1553,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83271CB-FC54-E142-86E3-37282DC63805}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1567,10 +1543,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1686,7 +1662,7 @@
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1697,7 +1673,7 @@
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B12" s="4">
         <v>2147483648</v>
@@ -1711,13 +1687,13 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1725,13 +1701,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1739,24 +1715,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1780,10 +1745,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1794,10 +1759,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -1903,13 +1868,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1917,13 +1882,13 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1942,13 +1907,13 @@
         <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1956,18 +1921,18 @@
         <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>22</v>
@@ -1981,10 +1946,10 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
@@ -1992,24 +1957,24 @@
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C17" s="2">
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C18" s="2">
         <v>50</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2035,10 +2000,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -2049,10 +2014,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -2155,13 +2120,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2169,13 +2134,13 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -2194,13 +2159,13 @@
         <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2208,18 +2173,18 @@
         <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>195</v>
@@ -2233,10 +2198,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
@@ -2255,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4411FE80-4885-BE47-8AEB-14F721AB3195}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -2268,10 +2233,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -2282,10 +2247,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -2388,13 +2353,13 @@
         <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2402,157 +2367,115 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17">
-        <v>26</v>
-      </c>
-      <c r="C17">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
+        <v>91</v>
+      </c>
+      <c r="B18">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21">
-        <v>51</v>
-      </c>
-      <c r="C21">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
         <v>35</v>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D65050-2AC1-D048-AE7F-FB396CC1A452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40602A1-896F-5941-89B9-BED2519E4035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="187">
   <si>
     <t>Extension</t>
   </si>
@@ -571,6 +571,21 @@
   </si>
   <si>
     <t>3013170411</t>
+  </si>
+  <si>
+    <t>PFSOFTV</t>
+  </si>
+  <si>
+    <t>0.1.0</t>
+  </si>
+  <si>
+    <t>pandorafits software version</t>
+  </si>
+  <si>
+    <t>TARG_RLL</t>
+  </si>
+  <si>
+    <t>Commanded roll [deg]</t>
   </si>
 </sst>
 </file>
@@ -936,6 +951,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1010,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1470,6 +1490,28 @@
       </c>
       <c r="D39" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>185</v>
+      </c>
+      <c r="C41">
+        <v>10.450973449999999</v>
+      </c>
+      <c r="D41" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1481,6 +1523,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZJc3hIa3ZIa3fIa3</t>
+          <t>AeWYBdWXAdWXAdWX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1324,16 +1324,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEQSTART</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>VISDALevel1HDUList</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1582,12 +1618,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JGLrLFKoJFKoJFKo</t>
+          <t>IJL2KHJ2IHJ2IHJ2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1641,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2044,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZemQfblQZblQdblQ</t>
+          <t>ZelTdekSZekSbekS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2067,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2406,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DfKGFeKFDeKFDeKF</t>
+          <t>CiJJEgJHCgJHCgJH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2429,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3272,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Upp7anm4Xnm4anm4</t>
+          <t>U3o7a0l7U0l7a0l7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3295,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4174,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FTaeFSYbFSabFSYb</t>
+          <t>EWaeEUWeEUaeEUWe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:29</t>
+          <t>HDU checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4197,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:29</t>
+          <t>data unit checksum updated 2026-01-07T18:03:50</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AeWYBdWXAdWXAdWX</t>
+          <t>M4YHM1X9M1XEM1X9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:55</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2454833</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1370,6 +1370,24 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-01-08T19:07:55.971</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1618,12 +1636,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IJL2KHJ2IHJ2IHJ2</t>
+          <t>HHJ3IHI1HHI1HHI1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1659,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2062,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZelTdekSZekSbekS</t>
+          <t>YfjUadjRZdjRadjR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2085,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2424,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CiJJEgJHCgJHCgJH</t>
+          <t>BgKHCgHHBgHHBgHH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2447,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3290,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U3o7a0l7U0l7a0l7</t>
+          <t>Y1m8a0k6T0k6Y0k6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3313,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4192,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EWaeEUWeEUaeEUWe</t>
+          <t>CUafFUVdCUZdCUZd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:50</t>
+          <t>HDU checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4215,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:50</t>
+          <t>data unit checksum updated 2026-01-08T14:07:56</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M4YHM1X9M1XEM1X9</t>
+          <t>Y682Z681Y681Y681</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:55</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:55</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-08T19:07:55.971</t>
+          <t>2026-01-16T17:19:55.247</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1636,12 +1636,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HHJ3IHI1HHI1HHI1</t>
+          <t>HKJ3IHI2HHI2HHI2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:56</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:56</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YfjUadjRZdjRadjR</t>
+          <t>YfjUaejSZejSaejS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:56</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:56</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BgKHCgHHBgHHBgHH</t>
+          <t>BjKKCgHHBgHHBgHH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:56</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:56</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y1m8a0k6T0k6Y0k6</t>
+          <t>Y1m8a1k7T1k7Y1k7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:56</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:56</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4192,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CUafFUVdCUZdCUZd</t>
+          <t>CXafFUVeCUZeCUZe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:56</t>
+          <t>HDU checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:56</t>
+          <t>data unit checksum updated 2026-01-16T10:19:55</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Y682Z681Y681Y681</t>
+          <t>Y5A2a360Z3A0a350</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-16T17:19:55.247</t>
+          <t>2026-01-16T22:40:08.582</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1636,12 +1636,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HKJ3IHI2HHI2HHI2</t>
+          <t>KFNqNFLoKFLoKFLo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YfjUaejSZejSaejS</t>
+          <t>ZdoSibmPZbmPfbmP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BjKKCgHHBgHHBgHH</t>
+          <t>EeMFHeLFEeLFEeLF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Y1m8a1k7T1k7Y1k7</t>
+          <t>Yoo6ano4Yno4ano4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4192,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CXafFUVeCUZeCUZe</t>
+          <t>GScdHSZbGSbbGSZb</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:55</t>
+          <t>HDU checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:55</t>
+          <t>data unit checksum updated 2026-01-16T15:40:08</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -484,12 +484,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROI_TABLE</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -499,12 +499,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEMP_TIME</t>
+          <t>VECTORS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -514,12 +514,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -529,12 +529,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STAR_TABLE</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,7 +830,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v3.05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -866,7 +866,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -884,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/01/04/2026-01-04__14-54-31_VisSci_LTT_1445_A_d050_n026_f00050_e000200000us.sp</t>
+          <t>/sssp/data/2026/05/08/2026-05-08__01-26-32_VisSci_WASP-178b_d050_n009_f11997_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -920,7 +920,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LTT_1445_A</t>
+          <t>WASP-178b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>45.46099853515625</t>
+          <t>227.27029418945312</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-16.594999313354492</t>
+          <t>-42.70498275756836</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -974,7 +974,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>239</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1100,7 +1100,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1118,7 +1118,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1136,7 +1136,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>820853698</t>
+          <t>831518875</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>503000000</t>
+          <t>976000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Y5A2a360Z3A0a350</t>
+          <t>AYZjAXWiAXWiAXWi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
@@ -1285,109 +1285,349 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>-42.70592109518633</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Executed DEC [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Commanded roll [deg]</t>
-        </is>
-      </c>
+          <t>0.4.8</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DPCSEQID</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Gaia DR3 6003809889735481856</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPC Obseravation Sequence ID</t>
+          <t>Gaia DR3 source ID</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2454833</t>
+          <t>227.27032703913977</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DPC Observation Sequence Start</t>
+          <t>Gaia DR3 RA in J2016</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>GAIADEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VISDALevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>-42.70496654225058</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Gaia DR3 DEC in J2016</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>PARALLAX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-16T22:40:08.582</t>
+          <t>2.424837486926974</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Gaia DR3 parallax</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PMRA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-10.24347465311499</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmra</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PMDEC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-5.63608880634272</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmdec</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2MASSID</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2MASS J15090488-4242178</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2MASS source ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>J_M</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>9.775</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2MASS j magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H_M</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>9.735</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2MASS h magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>K_M</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9.703</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>G_M</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>9.915789179327074</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gaia DR3 g magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BP_M</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9.950138912095703</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RP_M</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>9.833647482812413</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VISDALevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-10T18:51:12.984</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Pandora DPC Processing Time</t>
         </is>
       </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1400,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,7 +1740,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1514,7 +1754,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1528,7 +1768,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>239</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1636,12 +1876,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KFNqNFLoKFLoKFLo</t>
+          <t>N7fjO4djN4djN4dj</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
@@ -1654,42 +1894,546 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>336972189</t>
+          <t>512414433</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>1028.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>0.88552576580084</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-0.46459026905742</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>227.26835632324</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WCSAXES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Number of coordinate axes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CRPIX1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1028.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CRPIX2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PC1_1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.88552576580084</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PC1_2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.46459026905742</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-0.46459026905742</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.88552576580084</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEC--TAN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Declination, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>227.26835632324</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-42.705917358398</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>-42.705917358398</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COUNTS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PFSOFTV</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.4.8</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1702,7 +2446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,17 +2479,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -1802,7 +2546,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1820,7 +2564,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1873,12 +2617,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1895,12 +2639,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>StarROI_StartX</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>StarROI_StartX</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1913,12 +2657,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I21</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I21</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1926,17 +2670,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1944,17 +2688,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>StarROI_StartY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>StarROI_StartY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1962,17 +2706,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I21</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>I21</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1980,17 +2724,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1998,94 +2742,126 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TTYPE4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ROI_TABLE</t>
+          <t>Rotation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ROI_TABLE</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NUMSTARS</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Number of star ROIs in datacube</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STARDIMS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Dimension (N) of ROIs used to capture each star</t>
-        </is>
-      </c>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZdoSibmPZbmPfbmP</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DWPDDUODDUODDUOD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2007004370</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2773363002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,17 +2909,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2976,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2218,7 +2994,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>239</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2271,12 +3047,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2293,12 +3069,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ExposureStartTime_us</t>
+          <t>avg_ra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ExposureStartTime_us</t>
+          <t>avg_ra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2311,12 +3087,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I194</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I194</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -2324,17 +3100,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>avg_dec</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>avg_dec</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2342,17 +3118,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2360,17 +3136,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>avg_rot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>avg_rot</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2378,17 +3154,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2396,58 +3172,594 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TTYPE4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TEMP_TIME</t>
+          <t>err_ra</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TEMP_TIME</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EeMFHeLFEeLFEeLF</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>integration_time</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>integration_time</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TTYPE18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TFORM18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CdWaEdVZCdVaCdVW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2899297478</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1756454856</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
         </is>
       </c>
     </row>
@@ -2462,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2495,17 +3807,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -2517,17 +3829,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -2549,7 +3861,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -2562,12 +3874,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -2585,7 +3897,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -2603,7 +3915,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -2628,39 +3940,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>BSCALE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>BZERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2668,652 +3976,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>3AIn699k3AGk379k</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:13</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TBCOL2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TBCOL3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SDETMETH</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ATAITIME</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>820853698.503</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TAI Time for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AIMMEAN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>101.395988</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Image Mean after sigma clipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AIMSTD</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2.082717</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Image Standard Deviation after sigma clipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ATHRESH1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1st Star Detection Threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ATHRESH2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2nd Star Detection Threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AMINELLP</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Minimum ellipticity threshold for stars</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AMAXELLP</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maximum ellipticity threshold for stars</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AMINFLUX</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Minimum flux threshold for stars</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AMAXFLUX</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Maximum flux threshold for stars</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AXAXFLIP</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Was x-axis flipped for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ASCAL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0.7804</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Plate Scale for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ASCALRMS</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Plate Scale RMS error for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AROT</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>39.905</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Rotation for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AROTRMS</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0.054</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Rotation RMS error for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ARA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>45.46205</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Right Ascension for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ARARMS</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>9.699e-05</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Right Ascension RMS error for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ADEC</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-16.594716</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Declination for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ADECRMS</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0.00010624</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Declination RMS error for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AZERP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>21.76</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Magnitude Zeropoint for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AZERPRMS</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Magnitude Zeropoint RMS error for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AQUADS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Number of quads used for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AVERTS</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Number of quad sides used for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>APHSTARS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Number of photometric stars used for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>APOSTARS</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Number of position stars used for ast soln</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Yoo6ano4Yno4ano4</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3343168083</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>40960625</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:13</t>
         </is>
       </c>
     </row>
@@ -3328,7 +4042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,17 +4075,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -3383,17 +4097,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -3415,7 +4129,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -3428,12 +4142,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3446,12 +4160,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3469,7 +4183,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -3494,93 +4208,89 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>xCen</t>
-        </is>
-      </c>
+          <t>CONTAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>xCen</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flux not from the target in aperture in e/s</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
+          <t>COMPLTE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>1.0023387845494114</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fraction of flux from the target in aperture</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>TOTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>49183.14776120085</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Total flux expected in aperture in e/s</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>yCen</t>
-        </is>
-      </c>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>yCen</t>
+          <t>227.2702866086426</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3588,17 +4298,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>-42.7049828893777</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3606,17 +4312,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1029.8343703906676</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3624,17 +4326,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>1030.7790958612757</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3642,17 +4340,13 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>I50</t>
-        </is>
-      </c>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I50</t>
+          <t>6003809889735481856</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3660,562 +4354,108 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TBCOL3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ellipticity</t>
-        </is>
-      </c>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ellipticity</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TBCOL4</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NumPix</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NumPix</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>AfpSBdnQAdnQAdnQ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:13</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>I40</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I40</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TBCOL5</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CatalogRA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CatalogRA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TBCOL6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CatalogDec</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CatalogDec</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TBCOL7</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CatalogMag</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CatalogMag</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TBCOL8</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FittedRA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>FittedRA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TBCOL9</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FittedDec</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>FittedDec</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TBCOL10</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FittedMag</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>FittedMag</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TBCOL11</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CatalogStar</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CatalogStar</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>I10</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>I10</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TBCOL12</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>STAR_TABLE</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>STAR_TABLE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>name of extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>GScdHSZbGSbbGSZb</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:40:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>912660790</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:40:08</t>
+          <t>16777480</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:13</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -484,12 +485,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -499,12 +500,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VECTORS</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -514,12 +515,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -529,15 +530,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>VECTORS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>BinTableHDU</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>CompImageHDU</t>
         </is>
       </c>
-      <c r="C7" t="b">
+      <c r="C8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -552,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,7 +846,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.05</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,7 +900,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/05/08/2026-05-08__01-26-32_VisSci_WASP-178b_d050_n009_f11997_e000200000us.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__15-36-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -920,7 +936,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WASP-178b</t>
+          <t>WASP-18b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -938,7 +954,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>227.27029418945312</t>
+          <t>24.354568481445312</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +972,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-42.70498275756836</t>
+          <t>-45.677734375</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -974,7 +990,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +1008,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1046,7 +1062,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,7 +1080,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1082,7 +1098,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1226,7 +1242,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>831518875</t>
+          <t>836149075</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1244,7 +1260,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>976000000</t>
+          <t>394000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1262,12 +1278,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AYZjAXWiAXWiAXWi</t>
+          <t>e3HAh1F7e1FAe1F5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:04</t>
         </is>
       </c>
     </row>
@@ -1285,349 +1301,453 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>data unit checksum updated 2026-07-15T15:21:04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-42.70592109518633</t>
+          <t>24.354116273831984</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Executed DEC [deg]</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.4.8</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>140.7491762998052</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Executed roll [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GAIADR3</t>
+          <t>POS_Y</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gaia DR3 6003809889735481856</t>
+          <t>1029.8211329735532</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Gaia DR3 source ID</t>
+          <t>Y [row] Pixel position of target</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GAIARA</t>
+          <t>POS_X</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>227.27032703913977</t>
+          <t>1030.6817719775022</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Gaia DR3 RA in J2016</t>
+          <t>X [column] Pixel position of target</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GAIADEC</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-42.70496654225058</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Gaia DR3 DEC in J2016</t>
-        </is>
-      </c>
+          <t>0.5.0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PARALLAX</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.424837486926974</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Gaia DR3 parallax</t>
-        </is>
-      </c>
+          <t>2.6.0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PMRA</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-10.24347465311499</t>
+          <t>Gaia DR3 4955371367334610048</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmra</t>
+          <t>Gaia DR3 source ID</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PMDEC</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-5.63608880634272</t>
+          <t>24.3544669330396</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmdec</t>
+          <t>Gaia DR3 RA in J2016</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2MASSID</t>
+          <t>GAIADEC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2MASS J15090488-4242178</t>
+          <t>-45.6777908467995</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2MASS source ID</t>
+          <t>Gaia DR3 DEC in J2016</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J_M</t>
+          <t>PARALLAX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9.775</t>
+          <t>8.144292282321743</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2MASS j magnitude</t>
+          <t>Gaia DR3 parallax</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>H_M</t>
+          <t>PMRA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9.735</t>
+          <t>25.404449269627033</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2MASS h magnitude</t>
+          <t>Gaia DR3 pmra</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>K_M</t>
+          <t>PMDEC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9.703</t>
+          <t>20.47932580565009</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2MASS k magnitude</t>
+          <t>Gaia DR3 pmdec</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>G_M</t>
+          <t>2MASSID</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>9.915789179327074</t>
+          <t>2MASS J01372503-4540404</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Gaia DR3 g magnitude</t>
+          <t>2MASS source ID</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BP_M</t>
+          <t>J_M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9.950138912095703</t>
+          <t>8.409</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gaia DR3 bp magnitude</t>
+          <t>2MASS j magnitude</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RP_M</t>
+          <t>H_M</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9.833647482812413</t>
+          <t>8.231</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Gaia DR3 rp magnitude</t>
+          <t>2MASS h magnitude</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>K_M</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VISDALevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>8.131</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>G_M</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-06-10T18:51:12.984</t>
+          <t>9.173880843192613</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pandora DPC Processing Time</t>
+          <t>Gaia DR3 g magnitude</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BP_M</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>9.411079659286305</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>RP_M</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>8.777077857991749</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>TEFF</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
+          <t>6311.6724</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Gaia DR3 Teff</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LOGG</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.2654</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gaia DR3 logg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VISDALevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:21:04.416</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>Appended Vectors.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1640,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,7 +1825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1847,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1863,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1757,7 +1881,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1768,10 +1896,14 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1870,570 +2002,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N7fjO4djN4djN4dj</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
+          <t>COUNTS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>512414433</t>
+          <t>HMRhILRgHLRgHLRg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>HDU checksum updated 2026-07-15T15:21:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1028.0</t>
+          <t>1483695136</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PC1_1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.88552576580084</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PC2_1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-0.46459026905742</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0.00021750277777778</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>RA---TAN</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Right ascension, gnomonic projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>227.26835632324</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>WCSAXES</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Number of coordinate axes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CRPIX1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1028.0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CRPIX2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PC1_1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0.88552576580084</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PC1_2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0.46459026905742</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PC2_1</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-0.46459026905742</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PC2_2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0.88552576580084</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0.00021750277777778</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CDELT2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.00021750277777778</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CUNIT2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>RA---TAN</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Right ascension, gnomonic projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CTYPE2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DEC--TAN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Declination, gnomonic projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>227.26835632324</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CRVAL2</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-42.705917358398</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>-42.705917358398</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PFSOFTV</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0.4.8</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>data unit checksum updated 2026-07-15T15:21:04</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2446,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2479,17 +2093,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2115,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2523,12 +2137,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2546,322 +2160,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Time frame is JD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>93HpH2Go92GoE2Go</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PCOTemp</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PCOTemp</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DWPDDUODDUODDUOD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2773363002</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>1283685774</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:21:06</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2909,17 +2321,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -2931,12 +2343,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2953,12 +2365,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2976,790 +2388,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>second</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Exposure time unit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avg_ra</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>avg_ra</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>M9fWP6dWM6dWM6dW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avg_dec</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>avg_dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avg_rot</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>avg_rot</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>err_ra</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>err_ra</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>err_dec</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>err_dec</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>err_rot</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>err_rot</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>jd</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jd</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>integration_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>integration_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sep</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sep</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>earth_angle</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>earth_angle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>earth_illumination</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>earth_illumination</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sun_angle</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>sun_angle</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TTYPE15</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>visda_keepout</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>visda_keepout</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TFORM15</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TTYPE16</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nirda_keepout</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>nirda_keepout</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TFORM16</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TTYPE17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>posx</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>posx</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TFORM17</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TTYPE18</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>posy</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>posy</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TFORM18</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>VECTORS</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>VECTORS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CdWaEdVZCdVaCdVW</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1756454856</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>1904212305</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:21:06</t>
         </is>
       </c>
     </row>
@@ -3774,7 +2516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3807,17 +2549,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -3829,17 +2571,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -3861,7 +2603,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -3874,12 +2616,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -3892,12 +2634,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -3915,7 +2657,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -3940,35 +2682,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3976,58 +2722,216 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFORM1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3AIn699k3AGk379k</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:13</t>
-        </is>
-      </c>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>XCdSX9ZSXAbSX9ZS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>40960625</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:13</t>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>353690341</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:21:06</t>
         </is>
       </c>
     </row>
@@ -4042,7 +2946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,17 +2979,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -4097,17 +3001,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4129,7 +3033,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4142,12 +3046,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -4160,12 +3064,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -4183,7 +3087,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -4208,254 +3112,992 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Flux not from the target in aperture in e/s</t>
-        </is>
-      </c>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0023387845494114</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fraction of flux from the target in aperture</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TTYPE18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TFORM18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ErfdEoZdEofdEoZd</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2046082085</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BSCALE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>49183.14776120085</t>
+          <t>fA7ni75mfA5mf55m</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total flux expected in aperture in e/s</t>
+          <t>HDU checksum updated 2026-07-15T15:21:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>227.2702866086426</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-42.7049828893777</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1029.8343703906676</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1030.7790958612757</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GAIA_ID</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6003809889735481856</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AfpSBdnQAdnQAdnQ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>16777480</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:13</t>
+          <t>43516571</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:21:06</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,7 +900,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__15-36-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__07-32-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1116,7 +1116,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1242,7 +1242,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>836149075</t>
+          <t>836120035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1260,7 +1260,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>394000000</t>
+          <t>398000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1278,12 +1278,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>e3HAh1F7e1FAe1F5</t>
+          <t>7lfH9je97jeE7je9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:04</t>
+          <t>HDU checksum updated 2026-07-23T15:43:16</t>
         </is>
       </c>
     </row>
@@ -1301,422 +1301,422 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:04</t>
+          <t>data unit checksum updated 2026-07-23T15:43:16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>24.354116273831984</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Executed RA [deg]</t>
-        </is>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>140.7491762998052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Executed roll [deg]</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POS_Y</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1029.8211329735532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Y [row] Pixel position of target</t>
+          <t>Executed DEC [deg]</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POS_X</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1030.6817719775022</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>X [column] Pixel position of target</t>
+          <t>Executed roll [deg]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>POS_X</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.5.0</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>1030.6882545498438</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>X [column] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PRSOFTV</t>
+          <t>POS_Y</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.6.0</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>1029.8385208953534</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Y [row] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GAIADR3</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gaia DR3 4955371367334610048</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Gaia DR3 source ID</t>
-        </is>
-      </c>
+          <t>0.5.0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GAIARA</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>24.3544669330396</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Gaia DR3 RA in J2016</t>
-        </is>
-      </c>
+          <t>2.6.0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GAIADEC</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-45.6777908467995</t>
+          <t>Gaia DR3 4955371367334610048</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gaia DR3 DEC in J2016</t>
+          <t>Gaia DR3 source ID</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PARALLAX</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8.144292282321743</t>
+          <t>24.3544669330396</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Gaia DR3 parallax</t>
+          <t>Gaia DR3 RA in J2016</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PMRA</t>
+          <t>GAIADEC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25.404449269627033</t>
+          <t>-45.6777908467995</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmra</t>
+          <t>Gaia DR3 DEC in J2016</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PMDEC</t>
+          <t>PARALLAX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20.47932580565009</t>
+          <t>8.144292282321743</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmdec</t>
+          <t>Gaia DR3 parallax</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2MASSID</t>
+          <t>PMRA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2MASS J01372503-4540404</t>
+          <t>25.404449269627033</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2MASS source ID</t>
+          <t>Gaia DR3 pmra</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>J_M</t>
+          <t>PMDEC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.409</t>
+          <t>20.47932580565009</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2MASS j magnitude</t>
+          <t>Gaia DR3 pmdec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H_M</t>
+          <t>2MASSID</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.231</t>
+          <t>2MASS J01372503-4540404</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2MASS h magnitude</t>
+          <t>2MASS source ID</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>K_M</t>
+          <t>J_M</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8.131</t>
+          <t>8.409</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2MASS k magnitude</t>
+          <t>2MASS j magnitude</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>G_M</t>
+          <t>H_M</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9.173880843192613</t>
+          <t>8.231</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Gaia DR3 g magnitude</t>
+          <t>2MASS h magnitude</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BP_M</t>
+          <t>K_M</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9.411079659286305</t>
+          <t>8.131</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Gaia DR3 bp magnitude</t>
+          <t>2MASS k magnitude</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RP_M</t>
+          <t>G_M</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.777077857991749</t>
+          <t>9.173880843192613</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Gaia DR3 rp magnitude</t>
+          <t>Gaia DR3 g magnitude</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TEFF</t>
+          <t>BP_M</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6311.6724</t>
+          <t>9.411079659286305</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Gaia DR3 Teff</t>
+          <t>Gaia DR3 bp magnitude</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LOGG</t>
+          <t>RP_M</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4.2654</t>
+          <t>8.777077857991749</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Gaia DR3 logg</t>
+          <t>Gaia DR3 rp magnitude</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>TEFF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VISDALevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>6311.6724</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Gaia DR3 Teff</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>LOGG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-07-15T19:21:04.416</t>
+          <t>4.2654</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Pandora DPC Processing Time</t>
+          <t>Gaia DR3 logg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
+          <t>VISDALevel1HDUList</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1724,16 +1724,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>2026-07-23T19:43:16.665</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1744,10 +1748,24 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Appended Vectors.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1760,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,7 +1843,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1865,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -1863,11 +1881,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1881,11 +1895,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1899,11 +1909,7 @@
           <t>2280</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2002,52 +2008,394 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>7CVg9ASg7ASg7ASg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-23T15:43:17</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HMRhILRgHLRgHLRg</t>
+          <t>1483655666</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:04</t>
+          <t>data unit checksum updated 2026-07-23T15:43:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1483695136</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:04</t>
-        </is>
-      </c>
+          <t>Number of coordinate axes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CRPIX1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1028.0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CRPIX2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PC1_1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.77440241696784</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PC1_2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.63269336695936</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.63269336695936</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-0.77440241696784</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.00021750277777778</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEC--TAN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Declination, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>24.354110717773</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-45.676074981689</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-45.676074981689</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COUNTS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2250,12 +2598,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>93HpH2Go92GoE2Go</t>
+          <t>kE6Al937kE3Ak937</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+          <t>HDU checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2616,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1283685774</t>
+          <t>568084186</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+          <t>data unit checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2826,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M9fWP6dWM6dWM6dW</t>
+          <t>M7eXO5dUM5dUM5dU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+          <t>HDU checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2849,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+          <t>data unit checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2982,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2908,12 +3256,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XCdSX9ZSXAbSX9ZS</t>
+          <t>ZS5ZeS3YZS3YdS3Y</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+          <t>HDU checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -2926,12 +3274,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>353690341</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+          <t>data unit checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -3806,12 +4154,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ErfdEoZdEofdEoZd</t>
+          <t>6DN689L56CL569L5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+          <t>HDU checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -3824,12 +4172,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2046082085</t>
+          <t>1011054177</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+          <t>data unit checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4422,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fA7ni75mfA5mf55m</t>
+          <t>fA6lh45lfA5lf35l</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:21:06</t>
+          <t>HDU checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4445,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:21:06</t>
+          <t>data unit checksum updated 2026-07-23T15:43:18</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -485,12 +486,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>ROI_TABLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -500,12 +501,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXPTIME</t>
+          <t>TEMP_TIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -520,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -530,12 +531,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VECTORS</t>
+          <t>STAR_TABLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -545,15 +546,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -568,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,7 +862,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.06</t>
+          <t>v3.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -900,7 +916,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__07-32-32_VisSci_WASP-18b_d050_n009_f11400_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -936,7 +952,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WASP-18b</t>
+          <t>HD_200654</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -954,7 +970,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24.354568481445312</t>
+          <t>316.64697265625</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -972,7 +988,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-45.677734375</t>
+          <t>-49.965946197509766</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -990,7 +1006,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1008,7 +1024,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1062,7 +1078,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1080,7 +1096,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1098,7 +1114,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1116,7 +1132,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1134,7 +1150,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1152,7 +1168,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1242,7 +1258,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>836120035</t>
+          <t>840078298</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1260,7 +1276,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>398000000</t>
+          <t>706000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1278,12 +1294,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7lfH9je97jeE7je9</t>
+          <t>bWpQcWmObWmObWmO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:16</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1317,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:16</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -1322,450 +1338,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Executed RA [deg]</t>
-        </is>
-      </c>
+          <t>0.6.0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Executed DEC [deg]</t>
-        </is>
-      </c>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Executed roll [deg]</t>
-        </is>
-      </c>
+          <t>VISDALevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>POS_X</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1030.6882545498438</t>
+          <t>2026-08-26T01:26:17.569</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>X [column] Pixel position of target</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>POS_Y</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1029.8385208953534</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Y [row] Pixel position of target</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>PFSOFTV</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>0.5.0</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>PRSOFTV</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2.6.0</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>GAIADR3</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Gaia DR3 4955371367334610048</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Gaia DR3 source ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>GAIARA</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>24.3544669330396</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Gaia DR3 RA in J2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>GAIADEC</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>-45.6777908467995</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Gaia DR3 DEC in J2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>PARALLAX</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>8.144292282321743</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Gaia DR3 parallax</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>PMRA</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>25.404449269627033</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Gaia DR3 pmra</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>PMDEC</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>20.47932580565009</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Gaia DR3 pmdec</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2MASSID</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2MASS J01372503-4540404</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2MASS source ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>J_M</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>8.409</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2MASS j magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>H_M</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>8.231</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2MASS h magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>K_M</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>8.131</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2MASS k magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>G_M</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>9.173880843192613</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Gaia DR3 g magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BP_M</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>9.411079659286305</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Gaia DR3 bp magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>RP_M</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>8.777077857991749</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Gaia DR3 rp magnitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TEFF</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>6311.6724</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Gaia DR3 Teff</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>LOGG</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>4.2654</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Gaia DR3 logg</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PFCLASS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>VISDALevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>PFTIME</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-07-23T19:43:16.665</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
           <t>Pandora DPC Processing Time</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>COMMENT</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Appended Vectors.</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1778,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,7 +1506,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1892,7 +1520,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1906,7 +1534,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2014,12 +1642,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7CVg9ASg7ASg7ASg</t>
+          <t>ZkfNdkdLZkdLbkdL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:17</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2032,370 +1660,28 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1483655666</t>
+          <t>4098491597</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:17</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Number of coordinate axes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CRPIX1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1028.0</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CRPIX2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PC1_1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-0.77440241696784</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PC1_2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0.63269336695936</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PC2_1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>-0.63269336695936</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PC2_2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-0.77440241696784</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0.00021750277777778</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CDELT2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0.00021750277777778</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CUNIT2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>RA---TAN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Right ascension, gnomonic projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CTYPE2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DEC--TAN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Declination, gnomonic projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>24.354110717773</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CRVAL2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-45.676074981689</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-45.676074981689</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>ct</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2408,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2441,17 +1727,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>ASCII table extension</t>
         </is>
       </c>
     </row>
@@ -2463,12 +1749,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2485,12 +1771,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2508,120 +1794,290 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Time frame is JD</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>StarROI_StartX</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kE6Al937kE3Ak937</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-07-23T15:43:18</t>
-        </is>
-      </c>
+          <t>StarROI_StartX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TBCOL1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>StarROI_StartY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>StarROI_StartY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TBCOL2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ROI_TABLE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ROI_TABLE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>name of extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUMSTARS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Number of star ROIs in datacube</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STARDIMS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dimension (N) of ROIs used to capture each star</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3h9S5e8Q3e8Q3e8Q</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>568084186</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-07-23T15:43:18</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2222157953</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,17 +2125,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>ASCII table extension</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2147,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2713,12 +2169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2736,120 +2192,254 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>second</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Exposure time unit</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EXPTIME</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EXPTIME</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ExposureStartTime_us</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M7eXO5dUM5dUM5dU</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-07-23T15:43:18</t>
-        </is>
-      </c>
+          <t>ExposureStartTime_us</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>I194</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I194</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TBCOL1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TBCOL2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TEMP_TIME</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TEMP_TIME</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>name of extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eDTZeCRYeCRYeCRY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1904212305</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-07-23T15:43:18</t>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1002072366</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2897,17 +2487,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>ASCII table extension</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2554,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2982,7 +2572,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3035,12 +2625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3057,12 +2647,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RightAscension</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3075,12 +2665,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3088,17 +2678,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TBCOL1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RightAscension</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -3106,17 +2696,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Declination</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3124,17 +2714,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Declination</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Declination</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3142,17 +2732,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TFORM3</t>
+          <t>TBCOL2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3160,7 +2750,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTYPE4</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3178,17 +2768,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TFORM4</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3196,17 +2786,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TTYPE5</t>
+          <t>TBCOL3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PCOTemp</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PCOTemp</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -3214,72 +2804,508 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TFORM5</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>name of extension</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
+          <t>SDETMETH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Star Det Method (ConvertRaDecToXYWithWcs)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>ATAITIME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ZS5ZeS3YZS3YdS3Y</t>
+          <t>840078298.706</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:18</t>
+          <t>TAI Time for ast soln</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>AIMMEAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112.849083</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:18</t>
+          <t>Image Mean after sigma clipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AIMSTD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.010312</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Image Standard Deviation after sigma clipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ATHRESH1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1st Star Detection Threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ATHRESH2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2nd Star Detection Threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AMINELLP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Minimum ellipticity threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AMAXELLP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maximum ellipticity threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AMINFLUX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Minimum flux threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AMAXFLUX</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Maximum flux threshold for stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AXAXFLIP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Was x-axis flipped for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ASCAL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.7889</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plate Scale for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ASCALRMS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plate Scale RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AROT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>108.631</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rotation for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AROTRMS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rotation RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>316.645807</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Right Ascension for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ARARMS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6.443e-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Right Ascension RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ADEC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-49.964709</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Declination for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ADECRMS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9.975e-05</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Declination RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AZERP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Magnitude Zeropoint for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AZERPRMS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Magnitude Zeropoint RMS error for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AQUADS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Number of quads used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AVERTS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Number of quad sides used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APHSTARS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Number of photometric stars used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APOSTARS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Number of position stars used for ast soln</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VW6DYU69VU6CVU69</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3979163444</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -3327,17 +3353,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>TABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>ASCII table extension</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3420,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3412,7 +3438,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3465,12 +3491,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3487,12 +3513,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>avg_ra</t>
+          <t>xCen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>avg_ra</t>
+          <t>xCen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3505,12 +3531,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3518,17 +3544,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TBCOL1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>avg_dec</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>avg_dec</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -3536,17 +3562,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>yCen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>yCen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3554,17 +3580,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>avg_rot</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>avg_rot</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3572,17 +3598,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TFORM3</t>
+          <t>TBCOL2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3590,17 +3616,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTYPE4</t>
+          <t>TTYPE3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>err_ra</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>err_ra</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3608,17 +3634,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TFORM4</t>
+          <t>TFORM3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3626,17 +3652,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TTYPE5</t>
+          <t>TBCOL3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>err_dec</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>err_dec</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -3644,17 +3670,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TFORM5</t>
+          <t>TTYPE4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ellipticity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Ellipticity</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -3662,17 +3688,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TTYPE6</t>
+          <t>TFORM4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>err_rot</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>err_rot</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3680,17 +3706,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TFORM6</t>
+          <t>TBCOL4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3698,17 +3724,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TTYPE7</t>
+          <t>TTYPE5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jd</t>
+          <t>NumPix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jd</t>
+          <t>NumPix</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3716,17 +3742,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TFORM7</t>
+          <t>TFORM5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I40</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -3734,17 +3760,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TTYPE8</t>
+          <t>TBCOL5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>exptime</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>exptime</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -3752,17 +3778,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TFORM8</t>
+          <t>TTYPE6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CatalogRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CatalogRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -3770,17 +3796,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TTYPE9</t>
+          <t>TFORM6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>target_sep</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>target_sep</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3788,17 +3814,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TFORM9</t>
+          <t>TBCOL6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3806,17 +3832,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTYPE10</t>
+          <t>TTYPE7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>vitl_frames_count</t>
+          <t>CatalogDec</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>vitl_frames_count</t>
+          <t>CatalogDec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3824,17 +3850,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TFORM10</t>
+          <t>TFORM7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3842,17 +3868,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TTYPE11</t>
+          <t>TBCOL7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>vitl_missing_frames</t>
+          <t>166</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>vitl_missing_frames</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3860,17 +3886,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TFORM11</t>
+          <t>TTYPE8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CatalogMag</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CatalogMag</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3878,17 +3904,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TTYPE12</t>
+          <t>TFORM8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>earth_angle</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>earth_angle</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3896,17 +3922,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TFORM12</t>
+          <t>TBCOL8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3914,17 +3940,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TTYPE13</t>
+          <t>TTYPE9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>earth_illumination</t>
+          <t>FittedRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>earth_illumination</t>
+          <t>FittedRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3932,17 +3958,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TFORM13</t>
+          <t>TFORM9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3950,17 +3976,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TTYPE14</t>
+          <t>TBCOL9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sun_angle</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sun_angle</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3968,17 +3994,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TFORM14</t>
+          <t>TTYPE10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>FittedDec</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>FittedDec</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3986,17 +4012,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TTYPE15</t>
+          <t>TFORM10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>visda_keepout</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>visda_keepout</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -4004,17 +4030,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TFORM15</t>
+          <t>TBCOL10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>241</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -4022,17 +4048,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TTYPE16</t>
+          <t>TTYPE11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nirda_keepout</t>
+          <t>FittedMag</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nirda_keepout</t>
+          <t>FittedMag</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4040,17 +4066,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TFORM16</t>
+          <t>TFORM11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D25.17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4058,17 +4084,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TTYPE17</t>
+          <t>TBCOL11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>posx</t>
+          <t>266</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>posx</t>
+          <t>266</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4076,17 +4102,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TFORM17</t>
+          <t>TTYPE12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CatalogStar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CatalogStar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -4094,17 +4120,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TTYPE18</t>
+          <t>TFORM12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>posy</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>posy</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4112,17 +4138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TFORM18</t>
+          <t>TBCOL12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4135,15 +4161,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VECTORS</t>
+          <t>STAR_TABLE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VECTORS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>STAR_TABLE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>name of extension</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4154,12 +4184,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6DN689L56CL569L5</t>
+          <t>fU8jfR7jfR7jfR7j</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:18</t>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -4172,12 +4202,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1011054177</t>
+          <t>252246206</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:18</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4247,17 +4277,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4299,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4292,160 +4322,348 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Time frame is JD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>UeYkUZXkUdXkUZXk</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2620499513</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>second</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Exposure time unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>EXTNAME</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VgTaWZQTVfQYVZQY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>3501981725</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fA6lh45lfA5lf35l</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-07-23T15:43:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>43516571</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-07-23T15:43:18</t>
+          <t>data unit checksum updated 2026-08-25T21:26:17</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -1294,12 +1294,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bWpQcWmObWmObWmO</t>
+          <t>aYoQdVnOaVnOaVnO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:17.569</t>
+          <t>2026-09-08T18:41:17.517</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1642,12 +1642,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZkfNdkdLZkdLbkdL</t>
+          <t>ZjfMejeKZjeKdjeK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3h9S5e8Q3e8Q3e8Q</t>
+          <t>4g9R5d9P4d9P4d9P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eDTZeCRYeCRYeCRY</t>
+          <t>eCTYhBSXeBSXeBSX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VW6DYU69VU6CVU69</t>
+          <t>WV9BYT69WT6AWT69</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fU8jfR7jfR7jfR7j</t>
+          <t>fT8iiQ8ifQ8ifQ8i</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UeYkUZXkUdXkUZXk</t>
+          <t>UcYjXZYjUbYjUZYj</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VgTaWZQTVfQYVZQY</t>
+          <t>WeTaWZRRWdRXWZRX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:17</t>
+          <t>HDU checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:17</t>
+          <t>data unit checksum updated 2026-09-08T14:41:17</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -916,7 +916,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-35_VisSci_HD_200654_d050_n001_f05983_e000200000us.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -952,7 +952,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -970,7 +970,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>316.64697265625</t>
+          <t>307.8599548339844</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-49.965946197509766</t>
+          <t>39.9389762878418</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1006,7 +1006,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1024,7 +1024,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1258,7 +1258,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>840078298</t>
+          <t>840068292</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1276,7 +1276,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>706000000</t>
+          <t>8000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1294,12 +1294,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>aYoQdVnOaVnOaVnO</t>
+          <t>7ZJPAXGM8XGMAXGM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:20</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:17.517</t>
+          <t>2026-09-09T19:39:20.989</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1506,7 +1506,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1642,12 +1642,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZjfMejeKZjeKdjeK</t>
+          <t>7ASq78Qo7AQo77Qo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4098491597</t>
+          <t>2878043978</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2054,12 +2054,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4g9R5d9P4d9P4d9P</t>
+          <t>VNS2VKR1VKR1VKR1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2222157953</t>
+          <t>17102079</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2416,12 +2416,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eCTYhBSXeBSXeBSX</t>
+          <t>H6olH5okH5okH5ok</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1002072366</t>
+          <t>2032871319</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>840078298.706</t>
+          <t>840068292.008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2868,7 +2868,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>112.849083</t>
+          <t>189.042358</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2886,7 +2886,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.010312</t>
+          <t>19.295027</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3030,7 +3030,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7889</t>
+          <t>0.7899</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3048,7 +3048,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3066,7 +3066,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>108.631</t>
+          <t>247.711</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3084,7 +3084,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316.645807</t>
+          <t>307.860376</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3120,7 +3120,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.443e-05</t>
+          <t>8.489e-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3138,7 +3138,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-49.964709</t>
+          <t>39.939956</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3156,7 +3156,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9.975e-05</t>
+          <t>6.817e-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3174,7 +3174,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3192,7 +3192,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3210,7 +3210,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3228,7 +3228,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3246,7 +3246,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3282,12 +3282,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WV9BYT69WT6AWT69</t>
+          <t>UJK7a9J4XGJ4a9J4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -3300,12 +3300,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3979163444</t>
+          <t>1301764915</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4184,12 +4184,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fT8iiQ8ifQ8ifQ8i</t>
+          <t>5PLdAOJa8OJaAOJa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>252246206</t>
+          <t>632362844</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4412,12 +4412,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UcYjXZYjUbYjUZYj</t>
+          <t>T9lrW7joT7joT7jo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4430,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2620499513</t>
+          <t>1105499181</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4640,12 +4640,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WeTaWZRRWdRXWZRX</t>
+          <t>LlfZMkZZLkfZLkZZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:17</t>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3501981725</t>
+          <t>2708996155</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:17</t>
+          <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
       </c>
     </row>
